--- a/Output Files GPT-OSS 20B/rag_ablation_summary_by_decision_type.xlsx
+++ b/Output Files GPT-OSS 20B/rag_ablation_summary_by_decision_type.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -488,16 +488,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1.478833333333333</v>
+        <v>3.456166666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>1.58176292003106</v>
+        <v>3.759719858801539</v>
       </c>
       <c r="G2" t="n">
-        <v>0.816496580927726</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8660254037844387</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -505,12 +505,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -522,49 +522,19 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2.12787962962963</v>
+        <v>4.694499999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.183026472227605</v>
+        <v>4.72317884656792</v>
       </c>
       <c r="G3" t="n">
-        <v>0.816496580927726</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8660254037844387</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>nearest_neighbor_k3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nearest-neighbor prediction k=3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3688148148148149</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3875168733881066</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
